--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2025.xlsx
@@ -806,7 +806,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1119,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1489,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1554,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2473,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3331,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3640,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3705,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +3953,11 @@
           <t>77.163.842-2</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4018,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4083,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4209,11 @@
           <t>77.350.188-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4457,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +4949,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5014,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5445,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6425,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6551,11 @@
           <t>77.163.858-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6616,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6681,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6746,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7116,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7547,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7612,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7799,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8047,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8234,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8421,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8547,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8734,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8860,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9169,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9356,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9421,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9547,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9612,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9677,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9803,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9929,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11153,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11462,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11710,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11775,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12149,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12214,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12279,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12649,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +12836,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13328,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +13698,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +13946,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14011,11 @@
           <t>77.352.453-K</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14503,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +14690,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +14816,11 @@
           <t>77.352.453-K</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15064,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15312,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +15499,11 @@
           <t>77.094.046-K</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16052,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16178,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16243,11 @@
           <t>77.163.858-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16308,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +16617,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +16743,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +16808,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +16873,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +16938,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17064,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17190,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17316,11 @@
           <t>77.662.108-0</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +17930,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18117,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +19463,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +19833,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +19898,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20024,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20089,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20215,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +20585,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +20833,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21142,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/feb-2025.xlsx
@@ -1306,7 +1306,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2168,7 +2172,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2721,7 +2729,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3026,7 +3038,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3087,7 +3103,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10177,7 +10197,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
